--- a/relatorios/Mogo/Saldo Credito Carteira/04-2026.xlsx
+++ b/relatorios/Mogo/Saldo Credito Carteira/04-2026.xlsx
@@ -57,11 +57,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:D155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -469,10 +470,8 @@
           <t>03545781704</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
+      <c r="C2" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -491,10 +490,8 @@
           <t>04799289918</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>8,00</t>
-        </is>
+      <c r="C3" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -513,10 +510,8 @@
           <t>13007703760</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
+      <c r="C4" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -531,10 +526,8 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -553,10 +546,8 @@
           <t>07564017716</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>132,00</t>
-        </is>
+      <c r="C6" s="2" t="n">
+        <v>132</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -575,10 +566,8 @@
           <t>14991075793</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+      <c r="C7" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -597,10 +586,8 @@
           <t>10070804770</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+      <c r="C8" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -619,10 +606,8 @@
           <t>03153505985</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -637,10 +622,8 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -659,10 +642,8 @@
           <t>09929952721</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>81,00</t>
-        </is>
+      <c r="C11" s="2" t="n">
+        <v>81</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -677,10 +658,8 @@
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -699,10 +678,8 @@
           <t>14653796149</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -721,10 +698,8 @@
           <t>05260544765</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>203,50</t>
-        </is>
+      <c r="C14" s="2" t="n">
+        <v>203.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -743,10 +718,8 @@
           <t>83019014700</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>33,00</t>
-        </is>
+      <c r="C15" s="2" t="n">
+        <v>33</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -765,10 +738,8 @@
           <t>13051145742</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -787,10 +758,8 @@
           <t>83948660778</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>51,00</t>
-        </is>
+      <c r="C17" s="2" t="n">
+        <v>51</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -809,10 +778,8 @@
           <t>98514571753</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -831,10 +798,8 @@
           <t>80557635004</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+      <c r="C19" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -853,10 +818,8 @@
           <t>34422676768</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>42,00</t>
-        </is>
+      <c r="C20" s="2" t="n">
+        <v>42</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -875,10 +838,8 @@
           <t>08161767793</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -893,10 +854,8 @@
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -915,10 +874,8 @@
           <t>54525896191</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>4,50</t>
-        </is>
+      <c r="C23" s="2" t="n">
+        <v>4.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -937,10 +894,8 @@
           <t>12681934702</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>200,00</t>
-        </is>
+      <c r="C24" s="2" t="n">
+        <v>200</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -955,10 +910,8 @@
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -977,10 +930,8 @@
           <t>15304535774</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -999,10 +950,8 @@
           <t>12417854732</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1021,10 +970,8 @@
           <t>07532190773</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>268,50</t>
-        </is>
+      <c r="C28" s="2" t="n">
+        <v>268.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1043,10 +990,8 @@
           <t>14483239759</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1065,10 +1010,8 @@
           <t>08723620781</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1087,10 +1030,8 @@
           <t>06138299990</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1109,10 +1050,8 @@
           <t>12322870757</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>66,00</t>
-        </is>
+      <c r="C32" s="2" t="n">
+        <v>66</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1127,10 +1066,8 @@
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1149,10 +1086,8 @@
           <t>80158706749</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1171,10 +1106,8 @@
           <t>02533419737</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1189,10 +1122,8 @@
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>196,50</t>
-        </is>
+      <c r="C36" s="2" t="n">
+        <v>196.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1207,10 +1138,8 @@
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>7,50</t>
-        </is>
+      <c r="C37" s="2" t="n">
+        <v>7.5</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1225,10 +1154,8 @@
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>113,00</t>
-        </is>
+      <c r="C38" s="2" t="n">
+        <v>113</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1247,10 +1174,8 @@
           <t>13591948780</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1269,10 +1194,8 @@
           <t>83185887700</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>84,50</t>
-        </is>
+      <c r="C40" s="2" t="n">
+        <v>84.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1287,10 +1210,8 @@
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1301,2304 +1222,2133 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CRISTINA VACCARI MANGHI DE CARVALHO</t>
+          <t xml:space="preserve">Cleci Carvalho </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>02045628728</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>95662960704</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>150.8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>26843</t>
+          <t>29272</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CRISTINE RIBEIRO</t>
+          <t>CRISTINA VACCARI MANGHI DE CARVALHO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>34424725715</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>107,50</t>
-        </is>
+          <t>02045628728</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>26843</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cynthia Ozon Boghossian</t>
+          <t>CRISTINE RIBEIRO</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>01649775709</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>34424725715</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>107.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>17067</t>
+          <t>5015</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dani Féres</t>
+          <t>Cynthia Ozon Boghossian</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>04295601764</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>01649775709</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>17067</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Daniela Romão</t>
+          <t>Dani Féres</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>07194147769</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+          <t>04295601764</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22438</t>
+          <t>4757</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DEBORAH MATHIAS</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Daniela Romão</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>07194147769</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>22438</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">deca </t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>10046899774</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>36,50</t>
-        </is>
+          <t>DEBORAH MATHIAS</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>5125</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Denise Gerchenzon Braile</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+          <t xml:space="preserve">deca </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10046899774</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>36.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4559</t>
+          <t>23317</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eduardo Carneiro </t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>80401724700</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Denise Gerchenzon Braile</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>4559</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eliana F Lewkowicz </t>
+          <t xml:space="preserve">Eduardo Carneiro </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>46895540725</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>88,00</t>
-        </is>
+          <t>80401724700</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>6461</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elisa Werneck </t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
+          <t xml:space="preserve">Eliana F Lewkowicz </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>46895540725</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>88</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17754</t>
+          <t>8496</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ELISANGELA FERREIRA</t>
+          <t xml:space="preserve">Elisa Werneck </t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C53" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>17754</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Elizabeth Lins</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>09946681714</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>13,50</t>
-        </is>
+          <t>ELISANGELA FERREIRA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>4614</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ELIZABETH RIBEIRO MARQUES GOMES</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Elizabeth Lins</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>09946681714</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>13.5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6673</t>
+          <t>5849</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Estrela Regina</t>
+          <t>ELIZABETH RIBEIRO MARQUES GOMES</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>6673</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Felipe Castro (Jornalista)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>07836630722</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>260,61</t>
-        </is>
+          <t>Estrela Regina</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19411</t>
+          <t>9103</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fernanda De Souza Cardoso </t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>4,00</t>
-        </is>
+          <t>Felipe Castro (Jornalista)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>07836630722</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>99.64</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>29188</t>
+          <t>19411</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Fernanda Levy</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>08840263705</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">Fernanda De Souza Cardoso </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>7889</t>
+          <t>29188</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FERNANDA PRESTES TAFT</t>
+          <t>Fernanda Levy</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10789826780</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>08840263705</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>22769</t>
+          <t>7889</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Flávia Mara Miranda (21 98680-4614)</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>FERNANDA PRESTES TAFT</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>10789826780</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>4567</t>
+          <t>22769</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Gabriela Furtado</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>13921043786</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>33,00</t>
-        </is>
+          <t>Flávia Mara Miranda (21 98680-4614)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>4567</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">GABRIELA TEIXEIRA </t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Gabriela Furtado</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>13921043786</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>33</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>8382</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Galt Capital Consultoria de Investimentos LTDA</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>09175140000175</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">GABRIELA TEIXEIRA </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>7611</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Glaucia Delgado</t>
+          <t>Galt Capital Consultoria de Investimentos LTDA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>76011755704</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>33,00</t>
-        </is>
+          <t>09175140000175</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>9043</t>
+          <t>2393</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Gustavo Cavalcanti</t>
+          <t>Glaucia Delgado</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10286112426</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>76011755704</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>33</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26804</t>
+          <t>9043</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HYACINTA FARIAS</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr"/>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Gustavo Cavalcanti</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>10286112426</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>26804</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Irene Guerra Dantas</t>
+          <t>HYACINTA FARIAS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>1683</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Isabela Braga </t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>01101681780</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Irene Guerra Dantas</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>2004</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jane de Araújo Carvalho </t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr"/>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+          <t xml:space="preserve">Isabela Braga </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>01101681780</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>5453</t>
+          <t>6406</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jeannine Nacif </t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>01066953635</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">Jane de Araújo Carvalho </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>26824</t>
+          <t>5453</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>José André Cavalcanti da Silva</t>
+          <t xml:space="preserve">Jeannine Nacif </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>91984211404</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>37,00</t>
-        </is>
+          <t>01066953635</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>26824</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Juana Coimbra</t>
+          <t>José André Cavalcanti da Silva</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>07198489702</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>91984211404</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
+        <v>37</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10183</t>
+          <t>2588</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juliana de  Paula </t>
+          <t>Juana Coimbra</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12692213700</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>07198489702</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>10344</t>
+          <t>10183</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JULIANA DEL BARRIO</t>
+          <t xml:space="preserve">Juliana de  Paula </t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>02952676909</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>12692213700</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>10344</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Katya Goldenstein </t>
+          <t>JULIANA DEL BARRIO</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>97513946787</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>123,50</t>
-        </is>
+          <t>02952676909</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>3876</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laisa Cazelli Botelho </t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">Katya Goldenstein </t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>97513946787</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>123.5</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>2041</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Larissa Cysne</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>07917192784</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">Laisa Cazelli Botelho </t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>1735</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>laura schnoor</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>10715440713</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Larissa Cysne</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>21269</t>
+          <t>11234</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LEONARD DE QUEIROZ SOARES</t>
+          <t>laura schnoor</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>07925880708</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>10715440713</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9134</t>
+          <t>21269</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Letícia Martins da Cunha</t>
+          <t>LEONARD DE QUEIROZ SOARES</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>18829239798</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>07925880708</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>9134</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Lilian Fernandes Turlão</t>
+          <t>Letícia Martins da Cunha</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>13066198740</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>33,00</t>
-        </is>
+          <t>18829239798</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>12911</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Lívia Amaral</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Lilian Fernandes Turlão</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>13066198740</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>33</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>5077</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Lorena Campos Rachello</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>08453566666</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Lívia Amaral</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>24287</t>
+          <t>2271</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Luana  SINOTI</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Lorena Campos Rachello</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>08453566666</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>9408</t>
+          <t>24287</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Lucia Helena Mugayar Guedes Wambier</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>49124781720</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Luana  SINOTI</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>9408</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LUCIA MARIA BARROS DE SÁ</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Lucia Helena Mugayar Guedes Wambier</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>49124781720</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>138</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>LUCIANO ROCHA ARAUJO</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>00599805757</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>107,50</t>
-        </is>
+          <t>LUCIA MARIA BARROS DE SÁ</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>4663</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Marcela Freitas</t>
+          <t>LUCIANO ROCHA ARAUJO</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>07200011703</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>00599805757</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>107.5</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>6871</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Marcelo Lucena</t>
+          <t>Marcela Freitas</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>92617344720</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>188,50</t>
-        </is>
+          <t>07200011703</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>10760</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>MARCIA DANTONIO</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Marcelo Lucena</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>92617344720</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>188.5</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>22665</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Marcus Trovó</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>00000000000000</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>322,50</t>
-        </is>
+          <t>MARCIA DANTONIO</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>4713</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>MARIA AMELIA FREITAS DE PAULA PESSOA</t>
+          <t>Marcus Trovó</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>53594800768</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>00000000000000</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>322.5</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>1462</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Maria Antonieta</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr"/>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>MARIA AMELIA FREITAS DE PAULA PESSOA</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>53594800768</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>6577</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Maria Beatriz</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>85993905700</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Maria Antonieta</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>17027</t>
+          <t>4591</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maria Celina </t>
+          <t>Maria Beatriz</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>54944066600</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>85993905700</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>30238</t>
+          <t>17027</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>MARIA CLARA</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr"/>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">Maria Celina </t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>54944066600</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>30238</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Maria Clara tapajos</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>02163156702</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>MARIA CLARA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>17474</t>
+          <t>184</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Maria Constança Burity Carvalho</t>
+          <t>Maria Clara tapajos</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>00587800500</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>69,50</t>
-        </is>
+          <t>02163156702</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>17474</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MARIA DE JESUS PANTOJA DE MATOS</t>
+          <t>Maria Constança Burity Carvalho</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>79276113720</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>00587800500</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>69.5</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1810</t>
+          <t>10911</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Maria Fernanda Carvalho completo</t>
+          <t>MARIA DE JESUS PANTOJA DE MATOS</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>96702613768</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>79276113720</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10056</t>
+          <t>1810</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maria Isabel Simões Castanheira </t>
+          <t>Maria Fernanda Carvalho completo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>37653121772</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>33,00</t>
-        </is>
+          <t>96702613768</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>10056</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maria Isabella Albuquerque de Oliveira </t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Maria Gabriela Koblitz</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>02873657782</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>30771</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Maria Izabel Pena</t>
+          <t xml:space="preserve">Maria Isabel Simões Castanheira </t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>40677532768</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>5,00</t>
-        </is>
+          <t>37653121772</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>33</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>11180</t>
+          <t>2835</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Maria luiza</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>50450379787</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">Maria Isabella Albuquerque de Oliveira </t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>2213</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariana Miranda </t>
+          <t>Maria Izabel Pena</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>12398522741</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>7,00</t>
-        </is>
+          <t>40677532768</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>9893</t>
+          <t>11180</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mariana Pezzini </t>
+          <t>Maria luiza</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>01407230131</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>50450379787</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>24160</t>
+          <t>4156</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARILDA OLIVEIRA </t>
+          <t xml:space="preserve">Mariana Miranda </t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>34772081704</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>12398522741</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>7</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>9893</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MARÍLIA BONELLI RAMOS DE AZEVEDO</t>
+          <t xml:space="preserve">Mariana Pezzini </t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>07088076748</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>01407230131</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>24160</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marisa de Lima Viana </t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>213,50</t>
-        </is>
+          <t xml:space="preserve">MARILDA OLIVEIRA </t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>34772081704</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>18410</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marli Gomes Leal  </t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr"/>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>13,00</t>
-        </is>
+          <t>MARÍLIA BONELLI RAMOS DE AZEVEDO</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>07088076748</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>24259</t>
+          <t>161</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mayara Queiroz do Nascimento </t>
+          <t>Marisa de Lima Vianna</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>38217255830</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>225,00</t>
-        </is>
+          <t>60473533715</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>213.5</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11293</t>
+          <t>6640</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Mellissa Büchi</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>05213771700</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">Marli Gomes Leal  </t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" s="2" t="n">
+        <v>13</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>24259</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Michel Cosme Ferreira da Silva</t>
+          <t xml:space="preserve">Mayara Queiroz do Nascimento </t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>11896738788</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>38217255830</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="n">
+        <v>225</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>11293</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miguel Angelo Campagnac Rabello </t>
+          <t>Mellissa Büchi</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>80885179749</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>05213771700</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>16263</t>
+          <t>22062</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mirian </t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Michel Cosme Ferreira da Silva</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>11896738788</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>8733</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Nathalia Lira</t>
+          <t xml:space="preserve">Miguel Angelo Campagnac Rabello </t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>17172493702</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>188,50</t>
-        </is>
+          <t>80885179749</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>16263</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Nathália Regina Alves Dourado</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>40581106865</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+          <t xml:space="preserve">Mirian </t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>27175</t>
+          <t>4775</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Neusa Tamaio</t>
+          <t>Nathalia Lira</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>10546934803</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>17172493702</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="n">
+        <v>188.5</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>18571</t>
+          <t>17276</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Neuza Garcia</t>
+          <t>Nathália Regina Alves Dourado</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>83185550749</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>40581106865</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>27175</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Nicole Ascer</t>
+          <t>Neusa Tamaio</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>37490060753</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>10546934803</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>18571</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nicole Bentes Franca </t>
+          <t>Neuza Garcia</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>11936466775</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>83185550749</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>5759</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Odete Monteiro</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr"/>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Nicole Ascer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>37490060753</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>30405</t>
+          <t>4378</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Patrícia Braun </t>
+          <t xml:space="preserve">Nicole Bentes Franca </t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>52902056087</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>11936466775</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>20310</t>
+          <t>12226</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Paula Padilha</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>82911240782</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Odete Monteiro</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>30405</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Rachel de Sá Campos</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr"/>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t xml:space="preserve">Patrícia Braun </t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>52902056087</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>20310</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Rachel K Rianeli</t>
+          <t>Paula Padilha</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>04124846924</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>22,00</t>
-        </is>
+          <t>82911240782</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>2670</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>RAFAEL SAMPAIO PINCER</t>
+          <t>Rachel de Sá Campos</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>36,00</t>
-        </is>
+      <c r="C128" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>4755</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Regina Miranda</t>
+          <t>Rachel K Rianeli</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>15296784120</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>04124846924</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>22</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>8787</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Renata</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>05641000728</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>RAFAEL SAMPAIO PINCER</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" s="2" t="n">
+        <v>36</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>22675</t>
+          <t>1506</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Renata Couto da Silva</t>
+          <t>Regina Miranda</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>02544897708</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>- 203,50</t>
-        </is>
+          <t>15296784120</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>10948</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>RENATA CURI HAUEGEN</t>
+          <t>Renata</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>00538243694</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>05641000728</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>22675</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Renata Tenório</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr"/>
+          <t>Renata Couto da Silva</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>02544897708</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>0,00</t>
+          <t>- 203,50</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>13584</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>RITA SAMPAIO</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr"/>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>RENATA CURI HAUEGEN</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>00538243694</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4627</t>
+          <t>12781</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Rosangela Evangelista</t>
+          <t>Renata Tenório</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+      <c r="C135" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>7081</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosângela La porta </t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>66723388704</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>RITA SAMPAIO</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>29384</t>
+          <t>4627</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Roseane Teles Correia </t>
+          <t>Rosangela Evangelista</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>07386953780</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>74,00</t>
-        </is>
+          <t>00877866724</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>3929</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sérgio de Campante Santos</t>
+          <t xml:space="preserve">Rosângela La porta </t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>07405701701</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>2.880,00</t>
-        </is>
+          <t>66723388704</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>29384</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>sonia violeta rodrigues muller</t>
+          <t xml:space="preserve">Roseane Teles Correia </t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>10973552760</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>15,00</t>
-        </is>
+          <t>07386953780</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n">
+        <v>74</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>23202</t>
+          <t>9668</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Susana Gonçalves Arraes</t>
+          <t>Sérgio de Campante Santos</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>94034834749</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>30,00</t>
-        </is>
+          <t>07405701701</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>2880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>30407</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>SYMPOSIUM</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr"/>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>14,50</t>
-        </is>
+          <t>sonia violeta rodrigues muller</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>10973552760</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1708</t>
+          <t>23202</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Telda Rejane Batista Ramos</t>
+          <t>Susana Gonçalves Arraes</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>55494196020</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>94034834749</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>4754</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VERA A PEREIRA</t>
+          <t>SYMPOSIUM</t>
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+      <c r="C143" s="2" t="n">
+        <v>14.5</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>1708</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>VERA VIEIRA</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Telda Rejane Batista Ramos</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>55494196020</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>6906</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Veronica</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>07704080792</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+          <t>VERA A PEREIRA</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>2431</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Victor da Maceno Faro</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>04506704304</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>- 122,50</t>
-        </is>
+          <t>VERA VIEIRA</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>23258</t>
+          <t>16295</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Victor Hugo Teixeira correia</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Veronica</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>07704080792</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>10</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>11971</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitor Máximo </t>
+          <t>Victor da Maceno Faro</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>14210682730</t>
+          <t>04506704304</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>8,00</t>
+          <t>- 122,50</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>23258</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vitória Alecsandra Santos do Rosario </t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>11568489706</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>0,00</t>
-        </is>
+          <t>Victor Hugo Teixeira correia</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>6216</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>William Sandes</t>
+          <t xml:space="preserve">Vitor Máximo </t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>92986021204</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>10,00</t>
-        </is>
+          <t>14210682730</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>19916</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Yana Croce Ferreira de Carvalho</t>
+          <t xml:space="preserve">Vitória Alecsandra Santos do Rosario </t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>12482465788</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>6,00</t>
-        </is>
+          <t>11568489706</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>19825</t>
+          <t>9825</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>William Sandes</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>08183327788</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>11899</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
+          <t>Yana Croce Ferreira de Carvalho</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>12482465788</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>19825</t>
+        </is>
+      </c>
+    </row>
+    <row r="154"/>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>R$ 6.874,11</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>R$ 6.863,94</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
